--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0002T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.30469526257281</v>
+        <v>9.962012980168083</v>
       </c>
       <c r="D2" t="n">
-        <v>38.56972938583927</v>
+        <v>6.267581025198882</v>
       </c>
       <c r="E2" t="n">
-        <v>11.62434409986032</v>
+        <v>1.888955916227302</v>
       </c>
       <c r="F2" t="n">
-        <v>18.93801564431782</v>
+        <v>3.077427542201646</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.0686990896633</v>
+        <v>7.161163602070286</v>
       </c>
       <c r="D3" t="n">
-        <v>25.60980716748435</v>
+        <v>4.161593664716207</v>
       </c>
       <c r="E3" t="n">
-        <v>11.62434409986032</v>
+        <v>1.888955916227302</v>
       </c>
       <c r="F3" t="n">
-        <v>18.93801564431782</v>
+        <v>3.077427542201646</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.92367815378448</v>
+        <v>4.700097699989978</v>
       </c>
       <c r="D4" t="n">
-        <v>4.834264387942933</v>
+        <v>0.7855679630407266</v>
       </c>
       <c r="E4" t="n">
-        <v>11.62434409986032</v>
+        <v>1.888955916227302</v>
       </c>
       <c r="F4" t="n">
-        <v>18.93801564431782</v>
+        <v>3.077427542201646</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.31287637773094</v>
+        <v>8.013342411381277</v>
       </c>
       <c r="D5" t="n">
-        <v>56.77583645221095</v>
+        <v>9.226073423484278</v>
       </c>
       <c r="E5" t="n">
-        <v>11.62434409986032</v>
+        <v>1.888955916227302</v>
       </c>
       <c r="F5" t="n">
-        <v>18.93801564431782</v>
+        <v>3.077427542201646</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
